--- a/Employee_Reports_wi52/Mohammed Fahim Mohammed Laffir Q0576.xlsx
+++ b/Employee_Reports_wi52/Mohammed Fahim Mohammed Laffir Q0576.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-96</v>
+        <v>-104</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-98</v>
+        <v>-106</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-97</v>
+        <v>-105</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-84</v>
+        <v>-92</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-90</v>
+        <v>-98</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-99</v>
+        <v>-107</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-114</v>
+        <v>-122</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-83</v>
+        <v>-91</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1755,11 +1755,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1804,11 +1804,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-463</v>
+        <v>-471</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1902,11 +1902,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1951,11 +1951,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2000,11 +2000,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2049,11 +2049,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2077,20 +2077,20 @@
       <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>10-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>324</v>
+        <v>726</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
